--- a/artfynd/A 23017-2025 artfynd.xlsx
+++ b/artfynd/A 23017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1508,6 +1508,136 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125433199</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79428</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sydost om Valsebo, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>326404</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6551660</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Håbol</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23017-2025 artfynd.xlsx
+++ b/artfynd/A 23017-2025 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>125433199</v>
       </c>
       <c r="B10" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 23017-2025 artfynd.xlsx
+++ b/artfynd/A 23017-2025 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>125433199</v>
       </c>
       <c r="B10" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 23017-2025 artfynd.xlsx
+++ b/artfynd/A 23017-2025 artfynd.xlsx
@@ -1513,7 +1513,7 @@
         <v>125433199</v>
       </c>
       <c r="B10" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 23017-2025 artfynd.xlsx
+++ b/artfynd/A 23017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120447303</v>
+        <v>125433063</v>
       </c>
       <c r="B2" t="n">
-        <v>56559</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lilla Grundvattnet, Dls</t>
+          <t>Sydost om Valsebo, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>326544</v>
+        <v>326608</v>
       </c>
       <c r="R2" t="n">
-        <v>6551714</v>
+        <v>6551885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,56 +738,73 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Håbol</t>
+          <t>Nössemark</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rester av  fruktkropp, lila med lut</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Låga utan markkontakt # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Svensson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Örnborg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Fågelinventering Klinthögen 2024</t>
-        </is>
-      </c>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121654436</v>
+        <v>121654429</v>
       </c>
       <c r="B3" t="n">
-        <v>90765</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>326493</v>
+        <v>326620</v>
       </c>
       <c r="R3" t="n">
-        <v>6551731</v>
+        <v>6551552</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121654427</v>
+        <v>121654434</v>
       </c>
       <c r="B4" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>326663</v>
+        <v>326544</v>
       </c>
       <c r="R4" t="n">
-        <v>6551604</v>
+        <v>6551680</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,15 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121654441</v>
+        <v>121654436</v>
       </c>
       <c r="B5" t="n">
-        <v>92056</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>326652</v>
+        <v>326493</v>
       </c>
       <c r="R5" t="n">
-        <v>6551871</v>
+        <v>6551731</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,37 +1092,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121654429</v>
+        <v>121654445</v>
       </c>
       <c r="B6" t="n">
-        <v>92021</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>326620</v>
+        <v>326749</v>
       </c>
       <c r="R6" t="n">
-        <v>6551552</v>
+        <v>6551837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,15 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121654490</v>
+        <v>125432679</v>
       </c>
       <c r="B7" t="n">
-        <v>78632</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,34 +1200,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bjällhögen, Dls</t>
+          <t>Sydost om Valsebo, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>326506</v>
+        <v>326749</v>
       </c>
       <c r="R7" t="n">
-        <v>6551784</v>
+        <v>6551835</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,17 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>En väl draperad stam</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,33 +1279,49 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Levande träd # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Alfred Olofsson</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Edfors, Filip Myllyaho, Enviro Planning</t>
+          <t>Bård E. Andersen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121654431</v>
+        <v>121654441</v>
       </c>
       <c r="B8" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1317,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>326566</v>
+        <v>326652</v>
       </c>
       <c r="R8" t="n">
-        <v>6551657</v>
+        <v>6551871</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,11 +1389,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Gammalt födosöjsspår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,37 +1415,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121654434</v>
+        <v>121654427</v>
       </c>
       <c r="B9" t="n">
-        <v>90765</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1450,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>326544</v>
+        <v>326663</v>
       </c>
       <c r="R9" t="n">
-        <v>6551680</v>
+        <v>6551604</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,12 +1480,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,52 +1512,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125433199</v>
+        <v>121654490</v>
       </c>
       <c r="B10" t="n">
-        <v>79590</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sydost om Valsebo, Dls</t>
+          <t>Bjällhögen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>326404</v>
+        <v>326506</v>
       </c>
       <c r="R10" t="n">
-        <v>6551660</v>
+        <v>6551784</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,12 +1577,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En väl draperad stam</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1596,42 +1596,591 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stubbe # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125433199</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sydost om Valsebo, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>326404</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6551660</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Håbol</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stubbe # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Bård E. Andersen</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Bård E. Andersen</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121654431</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bjällhögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>326566</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6551657</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Håbol</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gammalt födosöjsspår</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Pia Edfors, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125437935</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sydost om Valsebo, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>326766</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6551830</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håbol</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125432538</v>
+      </c>
+      <c r="B14" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sydost om Valsebo, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>326766</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6551830</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Håbol</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Låga # Betula</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120447303</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lilla Grundvattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>326544</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6551714</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Håbol</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Andreas Ekedahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jonas Örnborg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Fågelinventering Klinthögen 2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23017-2025 artfynd.xlsx
+++ b/artfynd/A 23017-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125433063</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654429</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654434</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654436</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654445</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125432679</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1412,6 +1447,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654441</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654427</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654490</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125433199</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121654431</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1948,6 +2008,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125437935</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2075,6 +2140,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125432538</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2181,8 +2251,29 @@
           <t>Fågelinventering Klinthögen 2024</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120447303</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>